--- a/etf_holdings/2026-10-18_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-18_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:34</t>
+          <t>2026-10-18 20:48:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:34</t>
+          <t>2026-10-18 20:48:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:34</t>
+          <t>2026-10-18 20:48:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:36</t>
+          <t>2026-10-18 20:48:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:36</t>
+          <t>2026-10-18 20:48:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:36</t>
+          <t>2026-10-18 20:48:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:36</t>
+          <t>2026-10-18 20:48:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:36</t>
+          <t>2026-10-18 20:48:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:37</t>
+          <t>2026-10-18 20:48:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:37</t>
+          <t>2026-10-18 20:48:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:37</t>
+          <t>2026-10-18 20:48:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:37</t>
+          <t>2026-10-18 20:48:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:37</t>
+          <t>2026-10-18 20:48:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:37</t>
+          <t>2026-10-18 20:48:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-18 20:43:37</t>
+          <t>2026-10-18 20:48:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-18_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-18_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:39</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,40 +504,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>METAMETA PLATFORMS INC-CLASS A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.82%2420</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.89%406,000</t>
+          <t>5.66%81,400</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>5.66%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>406000</v>
+        <v>81400</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:39</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,40 +567,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>LITELUMENTUM HOLDINGS INC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.4%1090</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.09%667,000</t>
+          <t>5.42%65,999</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>5.42%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>667000</v>
+        <v>65999</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:39</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,40 +630,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>NVDANVIDIA CORP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.88%5165</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.00%134,000</t>
+          <t>4.78%233,100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>134000</v>
+        <v>233100</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:41</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,44 +689,44 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>AMDADVANCED MICRO DEVICES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.04%4250</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.00%165,000</t>
+          <t>4.32%81,379</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>165000</v>
+        <v>81379</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:41</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -752,44 +752,44 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>MSFTMICROSOFT CORP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.31%1635</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.99%420,000</t>
+          <t>4.12%80,920</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>420000</v>
+        <v>80920</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:41</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -815,44 +815,44 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>PLTRPALANTIR TECHNOLOGIES INC-A</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+7.46%3315</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+7.46%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.42%158,000</t>
+          <t>4.06%214,442</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>158000</v>
+        <v>214442</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:41</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -878,44 +878,44 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>BEBLOOM ENERGY CORP- A</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.74%1355</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.36%348,000</t>
+          <t>4.05%181,300</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>348000</v>
+        <v>181300</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:41</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -941,11 +941,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>SPCXSPACE EXPLORATION TECHN-CL A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -965,16 +965,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.30%236,200</t>
+          <t>3.60%256,528</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>236200</v>
+        <v>256528</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:42</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6857ADVANTEST CORP</t>
+          <t>SHOPSHOPIFY INC - CLASS A</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1028,16 +1028,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.22%59,400</t>
+          <t>3.43%204,100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>59400</v>
+        <v>204100</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:42</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1067,44 +1067,44 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>SNOWSNOWFLAKE INC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.54%1980</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.10%193,000</t>
+          <t>3.20%101,200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>193000</v>
+        <v>101200</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:42</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1130,11 +1130,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6920LASERTEC CORP</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1154,16 +1154,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.01%42,900</t>
+          <t>2.89%406,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>42900</v>
+        <v>406000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:42</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,44 +1193,44 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>DDOGDATADOG INC - CLASS A</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.1%275</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.77%967,000</t>
+          <t>2.46%98,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>967000</v>
+        <v>98000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:42</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1256,44 +1256,44 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>NETCLOUDFLARE INC - CLASS A</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7.32%557</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7.32%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.55%364,000</t>
+          <t>2.17%72,800</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>364000</v>
+        <v>72800</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:42</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1319,44 +1319,44 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.62%1245</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.54%156,000</t>
+          <t>2.09%667,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>156000</v>
+        <v>667000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-18 20:48:42</t>
+          <t>2026-10-18 21:17:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1382,44 +1382,44 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.48%7480</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.51%23,000</t>
+          <t>2.00%134,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23000</v>
+        <v>134000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
